--- a/Excel/Project/Freshmart/Cleaned/Cleaned_FreshMart_Suppliers.xlsx
+++ b/Excel/Project/Freshmart/Cleaned/Cleaned_FreshMart_Suppliers.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/AB6FF4EDD41B64DB/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{8D55D789-799A-4342-9A4D-F115E2E1F8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FCA3441-0B04-4B86-A7A1-B3669F6C8E4B}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{92638D98-D68F-4231-B062-D39A2529B642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{177B53D9-76F2-409F-AD36-2C97D054BA46}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{2595AD76-B8D3-4752-A969-AF72237C75E9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{2595AD76-B8D3-4752-A969-AF72237C75E9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Suppliers" sheetId="1" r:id="rId1"/>
     <sheet name="Data_Profiling" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="454">
   <si>
     <t>Active</t>
   </si>
@@ -1388,6 +1388,18 @@
   </si>
   <si>
     <t>Changed using Replace</t>
+  </si>
+  <si>
+    <t>The data type is Text</t>
+  </si>
+  <si>
+    <t>Complete Column</t>
+  </si>
+  <si>
+    <t>Changed to number</t>
+  </si>
+  <si>
+    <t>Phone2</t>
   </si>
 </sst>
 </file>
@@ -1465,10 +1477,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1477,18 +1489,12 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
+        <sz val="10"/>
+        <color auto="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF1F4E78"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1660,6 +1666,30 @@
         <scheme val="none"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E78"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1674,18 +1704,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{380C378D-E53A-470C-A602-E1EA393AA27D}" name="Table1" displayName="Table1" ref="A1:I86" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:I86" xr:uid="{380C378D-E53A-470C-A602-E1EA393AA27D}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{964BD182-399D-4205-8739-C38B970AC5B4}" name="Supplier_ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{CE3BFD58-C940-44A3-8027-B12EBA161E4F}" name="Supplier_Name" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{132A379E-1E2A-4FF6-B6C1-1716ED57A3C7}" name="Contact_Person" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{B7B5EA17-546B-4D52-8773-A1365E97D3DD}" name="Phone" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{93FF3684-4FAC-4CAD-8DA3-30148A7B10DB}" name="Email" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{478ED22D-5827-4227-BE0E-D7A3DFB2E20A}" name="City" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{B1AB76E5-E611-4D78-A994-13BCC2B94AB0}" name="Lead_Time_Days" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{223AB0D8-EE3D-4B71-A6F5-FB34B2ADEDE6}" name="Rating" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{4202B155-11D9-45EE-AF85-805863191FB1}" name="Status" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{380C378D-E53A-470C-A602-E1EA393AA27D}" name="Supplier" displayName="Supplier" ref="A1:J86" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J86" xr:uid="{380C378D-E53A-470C-A602-E1EA393AA27D}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{964BD182-399D-4205-8739-C38B970AC5B4}" name="Supplier_ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{CE3BFD58-C940-44A3-8027-B12EBA161E4F}" name="Supplier_Name" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{132A379E-1E2A-4FF6-B6C1-1716ED57A3C7}" name="Contact_Person" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{B7B5EA17-546B-4D52-8773-A1365E97D3DD}" name="Phone" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{1C642F38-7719-40DE-AD25-9DFAC15C8B4D}" name="Phone2" dataDxfId="0">
+      <calculatedColumnFormula>VALUE(D2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{93FF3684-4FAC-4CAD-8DA3-30148A7B10DB}" name="Email" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{478ED22D-5827-4227-BE0E-D7A3DFB2E20A}" name="City" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{B1AB76E5-E611-4D78-A994-13BCC2B94AB0}" name="Lead_Time_Days" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{223AB0D8-EE3D-4B71-A6F5-FB34B2ADEDE6}" name="Rating" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{4202B155-11D9-45EE-AF85-805863191FB1}" name="Status" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2008,20 +2041,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1D1A42-F60C-45A4-A29B-676B188C117D}">
-  <dimension ref="A1:I86"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J86"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.453125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="17.36328125" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
     <col min="5" max="5" width="39" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="18.81640625" customWidth="1"/>
+    <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
     <col min="8" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>441</v>
       </c>
@@ -2035,22 +2068,25 @@
         <v>438</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>432</v>
       </c>
@@ -2063,23 +2099,27 @@
       <c r="D2" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="1">
+        <f t="shared" ref="E2:E33" si="0">VALUE(D2)</f>
+        <v>9826600539</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>4</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>4.3</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>427</v>
       </c>
@@ -2092,23 +2132,27 @@
       <c r="D3" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="1">
+        <f t="shared" si="0"/>
+        <v>9349817734</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>2.7</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>422</v>
       </c>
@@ -2121,23 +2165,27 @@
       <c r="D4" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="1">
+        <f t="shared" si="0"/>
+        <v>9732719211</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>8</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>3.1</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>417</v>
       </c>
@@ -2150,23 +2198,27 @@
       <c r="D5" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>9398362082</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>13</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>3.6</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>412</v>
       </c>
@@ -2179,23 +2231,27 @@
       <c r="D6" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="1">
+        <f t="shared" si="0"/>
+        <v>9469319644</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>8</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>2.7</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>407</v>
       </c>
@@ -2208,23 +2264,27 @@
       <c r="D7" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>9506448196</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>45</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>402</v>
       </c>
@@ -2237,23 +2297,27 @@
       <c r="D8" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>9174684276</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>11</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>3</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>397</v>
       </c>
@@ -2266,23 +2330,27 @@
       <c r="D9" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>9398471886</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>15</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>2.8</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>392</v>
       </c>
@@ -2295,23 +2363,27 @@
       <c r="D10" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>9853573823</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>4.2</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>387</v>
       </c>
@@ -2324,23 +2396,27 @@
       <c r="D11" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
+        <v>9596348124</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>13</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>3.1</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>383</v>
       </c>
@@ -2353,23 +2429,27 @@
       <c r="D12" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="1">
+        <f t="shared" si="0"/>
+        <v>9924970419</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>5</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>4.2</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>378</v>
       </c>
@@ -2382,23 +2462,27 @@
       <c r="D13" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
+        <v>9326541099</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>8</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>3.2</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>373</v>
       </c>
@@ -2411,21 +2495,25 @@
       <c r="D14" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>9790256940</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="1">
+      <c r="G14" s="3"/>
+      <c r="H14" s="1">
         <v>8</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>4.7</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>368</v>
       </c>
@@ -2438,23 +2526,27 @@
       <c r="D15" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>9727694430</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>10</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>3.2</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>363</v>
       </c>
@@ -2467,23 +2559,27 @@
       <c r="D16" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="1">
+        <f t="shared" si="0"/>
+        <v>9911514914</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>10</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>3.7</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>358</v>
       </c>
@@ -2496,23 +2592,27 @@
       <c r="D17" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>9509760584</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>11</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>2.7</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>353</v>
       </c>
@@ -2525,23 +2625,27 @@
       <c r="D18" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="1">
+        <f t="shared" si="0"/>
+        <v>9831980933</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>12</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>4.3</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>347</v>
       </c>
@@ -2554,23 +2658,27 @@
       <c r="D19" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>9587182120</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>6</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>3.6</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>342</v>
       </c>
@@ -2583,23 +2691,27 @@
       <c r="D20" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="1">
+        <f t="shared" si="0"/>
+        <v>9771410971</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>10</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>4.8</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>337</v>
       </c>
@@ -2612,23 +2724,27 @@
       <c r="D21" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="1">
+        <f t="shared" si="0"/>
+        <v>9679153816</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>7</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>332</v>
       </c>
@@ -2641,23 +2757,27 @@
       <c r="D22" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="1">
+        <f t="shared" si="0"/>
+        <v>9489747629</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>9</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>2.5</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>327</v>
       </c>
@@ -2670,23 +2790,27 @@
       <c r="D23" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="1">
+        <f t="shared" si="0"/>
+        <v>9174316370</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>13</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>3.7</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J23" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>322</v>
       </c>
@@ -2699,23 +2823,27 @@
       <c r="D24" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="1">
+        <f t="shared" si="0"/>
+        <v>9666585408</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>10</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>2.9</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J24" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>317</v>
       </c>
@@ -2728,23 +2856,27 @@
       <c r="D25" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="1">
+        <f t="shared" si="0"/>
+        <v>9821218382</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>13</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>3.3</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J25" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>312</v>
       </c>
@@ -2757,23 +2889,27 @@
       <c r="D26" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="1">
+        <f t="shared" si="0"/>
+        <v>9463016614</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>5</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>3.1</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J26" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>307</v>
       </c>
@@ -2786,23 +2922,27 @@
       <c r="D27" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="1">
+        <f t="shared" si="0"/>
+        <v>9163215224</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>3</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>4.3</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J27" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>302</v>
       </c>
@@ -2815,23 +2955,27 @@
       <c r="D28" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="1">
+        <f t="shared" si="0"/>
+        <v>9621209849</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>5</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>3.2</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>297</v>
       </c>
@@ -2844,23 +2988,27 @@
       <c r="D29" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="1">
+        <f t="shared" si="0"/>
+        <v>9967043303</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>5</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>4.5</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J29" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>292</v>
       </c>
@@ -2873,23 +3021,27 @@
       <c r="D30" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="1">
+        <f t="shared" si="0"/>
+        <v>9882839238</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>8</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>3.5</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J30" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>287</v>
       </c>
@@ -2902,23 +3054,27 @@
       <c r="D31" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="1">
+        <f t="shared" si="0"/>
+        <v>9366992705</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>14</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>4.7</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>282</v>
       </c>
@@ -2931,21 +3087,25 @@
       <c r="D32" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="1">
+        <f t="shared" si="0"/>
+        <v>9180943908</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="1">
+      <c r="G32" s="3"/>
+      <c r="H32" s="1">
         <v>6</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <v>3.7</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J32" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>277</v>
       </c>
@@ -2958,23 +3118,27 @@
       <c r="D33" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="1">
+        <f t="shared" si="0"/>
+        <v>9997677788</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>12</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>5</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>272</v>
       </c>
@@ -2987,23 +3151,27 @@
       <c r="D34" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="1">
+        <f t="shared" ref="E34:E65" si="1">VALUE(D34)</f>
+        <v>9530613729</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="G34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>9</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <v>3.7</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>267</v>
       </c>
@@ -3016,23 +3184,27 @@
       <c r="D35" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="1">
+        <f t="shared" si="1"/>
+        <v>9884374109</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G35" s="1">
+      <c r="H35" s="1">
         <v>6</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <v>3.6</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J35" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>262</v>
       </c>
@@ -3045,23 +3217,27 @@
       <c r="D36" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="1">
+        <f t="shared" si="1"/>
+        <v>9721890096</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>5</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J36" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>257</v>
       </c>
@@ -3074,23 +3250,27 @@
       <c r="D37" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="1">
+        <f t="shared" si="1"/>
+        <v>9670292350</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <v>11</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <v>3.7</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J37" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>253</v>
       </c>
@@ -3103,23 +3283,27 @@
       <c r="D38" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="1">
+        <f t="shared" si="1"/>
+        <v>9825003955</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G38" s="1">
+      <c r="H38" s="1">
         <v>3</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <v>4</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J38" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>248</v>
       </c>
@@ -3132,23 +3316,27 @@
       <c r="D39" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="1">
+        <f t="shared" si="1"/>
+        <v>9188029013</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>11</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <v>2.6</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J39" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>243</v>
       </c>
@@ -3161,23 +3349,27 @@
       <c r="D40" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="1">
+        <f t="shared" si="1"/>
+        <v>9437352358</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <v>5</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <v>4.2</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J40" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>238</v>
       </c>
@@ -3190,23 +3382,27 @@
       <c r="D41" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="1">
+        <f t="shared" si="1"/>
+        <v>9670292350</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <v>9</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <v>3.3</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J41" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>233</v>
       </c>
@@ -3219,23 +3415,27 @@
       <c r="D42" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="1">
+        <f t="shared" si="1"/>
+        <v>9384756779</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G42" s="1">
+      <c r="H42" s="1">
         <v>10</v>
       </c>
-      <c r="H42" s="1">
+      <c r="I42" s="1">
         <v>3</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J42" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>228</v>
       </c>
@@ -3248,23 +3448,27 @@
       <c r="D43" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="1">
+        <f t="shared" si="1"/>
+        <v>9570497096</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="1">
+      <c r="H43" s="1">
         <v>7</v>
       </c>
-      <c r="H43" s="1">
+      <c r="I43" s="1">
         <v>3.2</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J43" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>223</v>
       </c>
@@ -3277,23 +3481,27 @@
       <c r="D44" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="1">
+        <f t="shared" si="1"/>
+        <v>9421455482</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G44" s="1">
+      <c r="H44" s="1">
         <v>12</v>
       </c>
-      <c r="H44" s="1">
+      <c r="I44" s="1">
         <v>4.5</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J44" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>218</v>
       </c>
@@ -3306,23 +3514,27 @@
       <c r="D45" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="1">
+        <f t="shared" si="1"/>
+        <v>9266910922</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>3</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J45" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>213</v>
       </c>
@@ -3335,23 +3547,27 @@
       <c r="D46" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="1">
+        <f t="shared" si="1"/>
+        <v>9383450553</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="1">
+      <c r="H46" s="1">
         <v>12</v>
       </c>
-      <c r="H46" s="1">
+      <c r="I46" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J46" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>208</v>
       </c>
@@ -3364,23 +3580,27 @@
       <c r="D47" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="1">
+        <f t="shared" si="1"/>
+        <v>9103807155</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="1">
+      <c r="H47" s="1">
         <v>15</v>
       </c>
-      <c r="H47" s="1">
+      <c r="I47" s="1">
         <v>3.2</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J47" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>203</v>
       </c>
@@ -3393,23 +3613,27 @@
       <c r="D48" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="1">
+        <f t="shared" si="1"/>
+        <v>9702269164</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G48" s="1">
+      <c r="H48" s="1">
         <v>10</v>
       </c>
-      <c r="H48" s="1">
+      <c r="I48" s="1">
         <v>4.3</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J48" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>198</v>
       </c>
@@ -3422,23 +3646,27 @@
       <c r="D49" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="1">
+        <f t="shared" si="1"/>
+        <v>9693269304</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G49" s="1">
+      <c r="H49" s="1">
         <v>15</v>
       </c>
-      <c r="H49" s="1">
+      <c r="I49" s="1">
         <v>3.4</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J49" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>193</v>
       </c>
@@ -3451,23 +3679,27 @@
       <c r="D50" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="1">
+        <f t="shared" si="1"/>
+        <v>9367930513</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G50" s="1">
+      <c r="H50" s="1">
         <v>7</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <v>3</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J50" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>188</v>
       </c>
@@ -3480,23 +3712,27 @@
       <c r="D51" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="1">
+        <f t="shared" si="1"/>
+        <v>9958872154</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G51" s="1">
+      <c r="H51" s="1">
         <v>5</v>
       </c>
-      <c r="H51" s="1">
+      <c r="I51" s="1">
         <v>4.7</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J51" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>183</v>
       </c>
@@ -3509,23 +3745,27 @@
       <c r="D52" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="1">
+        <f t="shared" si="1"/>
+        <v>9961393416</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G52" s="1">
+      <c r="H52" s="1">
         <v>14</v>
       </c>
-      <c r="H52" s="1">
+      <c r="I52" s="1">
         <v>4.8</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J52" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>178</v>
       </c>
@@ -3538,23 +3778,27 @@
       <c r="D53" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="1">
+        <f t="shared" si="1"/>
+        <v>9510751046</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="G53" s="1">
+      <c r="H53" s="1">
         <v>14</v>
       </c>
-      <c r="H53" s="1">
+      <c r="I53" s="1">
         <v>4.3</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J53" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>173</v>
       </c>
@@ -3567,23 +3811,27 @@
       <c r="D54" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="1">
+        <f t="shared" si="1"/>
+        <v>9344378798</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="G54" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G54" s="1">
+      <c r="H54" s="1">
         <v>15</v>
       </c>
-      <c r="H54" s="1">
+      <c r="I54" s="1">
         <v>4.5</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J54" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>168</v>
       </c>
@@ -3596,23 +3844,27 @@
       <c r="D55" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="1">
+        <f t="shared" si="1"/>
+        <v>9930353157</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G55" s="1">
+      <c r="H55" s="1">
         <v>15</v>
       </c>
-      <c r="H55" s="1">
+      <c r="I55" s="1">
         <v>2.7</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J55" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>163</v>
       </c>
@@ -3625,23 +3877,27 @@
       <c r="D56" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="1">
+        <f t="shared" si="1"/>
+        <v>9223847257</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="G56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G56" s="1">
+      <c r="H56" s="1">
         <v>7</v>
       </c>
-      <c r="H56" s="1">
+      <c r="I56" s="1">
         <v>4.8</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J56" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>158</v>
       </c>
@@ -3654,23 +3910,27 @@
       <c r="D57" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="1">
+        <f t="shared" si="1"/>
+        <v>9882269302</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="G57" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G57" s="1">
+      <c r="H57" s="1">
         <v>11</v>
       </c>
-      <c r="H57" s="1">
+      <c r="I57" s="1">
         <v>3.6</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J57" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>153</v>
       </c>
@@ -3683,23 +3943,27 @@
       <c r="D58" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="1">
+        <f t="shared" si="1"/>
+        <v>9147659674</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G58" s="1">
+      <c r="H58" s="1">
         <v>11</v>
       </c>
-      <c r="H58" s="1">
+      <c r="I58" s="1">
         <v>3</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J58" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>148</v>
       </c>
@@ -3712,23 +3976,27 @@
       <c r="D59" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="1">
+        <f t="shared" si="1"/>
+        <v>9813219781</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G59" s="1">
+      <c r="H59" s="1">
         <v>7</v>
       </c>
-      <c r="H59" s="1">
+      <c r="I59" s="1">
         <v>3.6</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J59" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>143</v>
       </c>
@@ -3741,23 +4009,27 @@
       <c r="D60" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="1">
+        <f t="shared" si="1"/>
+        <v>9538508549</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="G60" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G60" s="1">
+      <c r="H60" s="1">
         <v>10</v>
       </c>
-      <c r="H60" s="1">
+      <c r="I60" s="1">
         <v>3.3</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J60" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>138</v>
       </c>
@@ -3770,23 +4042,27 @@
       <c r="D61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="1">
+        <f t="shared" si="1"/>
+        <v>9286860433</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G61" s="1">
+      <c r="H61" s="1">
         <v>12</v>
       </c>
-      <c r="H61" s="1">
+      <c r="I61" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J61" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>133</v>
       </c>
@@ -3799,23 +4075,27 @@
       <c r="D62" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="1">
+        <f t="shared" si="1"/>
+        <v>9561588882</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="G62" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G62" s="1">
+      <c r="H62" s="1">
         <v>6</v>
       </c>
-      <c r="H62" s="1">
+      <c r="I62" s="1">
         <v>3.2</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J62" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>127</v>
       </c>
@@ -3828,23 +4108,27 @@
       <c r="D63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="1">
+        <f t="shared" si="1"/>
+        <v>9608079792</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="G63" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G63" s="1">
+      <c r="H63" s="1">
         <v>12</v>
       </c>
-      <c r="H63" s="1">
+      <c r="I63" s="1">
         <v>3</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J63" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>122</v>
       </c>
@@ -3857,23 +4141,27 @@
       <c r="D64" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="1">
+        <f t="shared" si="1"/>
+        <v>9906528433</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G64" s="1">
+      <c r="H64" s="1">
         <v>7</v>
       </c>
-      <c r="H64" s="1">
+      <c r="I64" s="1">
         <v>2.7</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J64" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>117</v>
       </c>
@@ -3884,23 +4172,27 @@
       <c r="D65" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="1">
+        <f t="shared" si="1"/>
+        <v>9610173760</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G65" s="1">
+      <c r="H65" s="1">
         <v>2</v>
       </c>
-      <c r="H65" s="1">
+      <c r="I65" s="1">
         <v>3.1</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J65" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>113</v>
       </c>
@@ -3913,23 +4205,27 @@
       <c r="D66" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="1">
+        <f t="shared" ref="E66:E97" si="2">VALUE(D66)</f>
+        <v>9512293741</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G66" s="1">
+      <c r="H66" s="1">
         <v>5</v>
       </c>
-      <c r="H66" s="1">
+      <c r="I66" s="1">
         <v>4.3</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J66" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>109</v>
       </c>
@@ -3942,23 +4238,27 @@
       <c r="D67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="1">
+        <f t="shared" si="2"/>
+        <v>9214447237</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G67" s="1">
+      <c r="H67" s="1">
         <v>14</v>
       </c>
-      <c r="H67" s="1">
+      <c r="I67" s="1">
         <v>4.7</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J67" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>103</v>
       </c>
@@ -3971,23 +4271,27 @@
       <c r="D68" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="1">
+        <f t="shared" si="2"/>
+        <v>9230307805</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="G68" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G68" s="1">
+      <c r="H68" s="1">
         <v>2</v>
       </c>
-      <c r="H68" s="1">
+      <c r="I68" s="1">
         <v>3.9</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J68" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>98</v>
       </c>
@@ -4000,23 +4304,27 @@
       <c r="D69" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="1">
+        <f t="shared" si="2"/>
+        <v>9642001424</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="G69" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G69" s="1">
+      <c r="H69" s="1">
         <v>11</v>
       </c>
-      <c r="H69" s="1">
+      <c r="I69" s="1">
         <v>4.5</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J69" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>92</v>
       </c>
@@ -4029,23 +4337,27 @@
       <c r="D70" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="1">
+        <f t="shared" si="2"/>
+        <v>9583258726</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="G70" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G70" s="1">
+      <c r="H70" s="1">
         <v>13</v>
       </c>
-      <c r="H70" s="1">
+      <c r="I70" s="1">
         <v>4.7</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J70" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>86</v>
       </c>
@@ -4058,23 +4370,27 @@
       <c r="D71" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="1">
+        <f t="shared" si="2"/>
+        <v>9394846763</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="G71" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G71" s="1">
+      <c r="H71" s="1">
         <v>9</v>
       </c>
-      <c r="H71" s="1">
+      <c r="I71" s="1">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J71" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>81</v>
       </c>
@@ -4087,23 +4403,27 @@
       <c r="D72" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="1">
+        <f t="shared" si="2"/>
+        <v>9186519602</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="G72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G72" s="1">
+      <c r="H72" s="1">
         <v>7</v>
       </c>
-      <c r="H72" s="1">
+      <c r="I72" s="1">
         <v>4.7</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J72" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>76</v>
       </c>
@@ -4116,23 +4436,27 @@
       <c r="D73" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="1">
+        <f t="shared" si="2"/>
+        <v>9455281184</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G73" s="1">
+      <c r="H73" s="1">
         <v>3</v>
       </c>
-      <c r="H73" s="1">
+      <c r="I73" s="1">
         <v>3.5</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J73" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>71</v>
       </c>
@@ -4145,23 +4469,27 @@
       <c r="D74" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="1">
+        <f t="shared" si="2"/>
+        <v>9727150493</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G74" s="1">
+      <c r="H74" s="1">
         <v>8</v>
       </c>
-      <c r="H74" s="1">
+      <c r="I74" s="1">
         <v>4.8</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J74" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4174,23 +4502,27 @@
       <c r="D75" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="1">
+        <f t="shared" si="2"/>
+        <v>9477698143</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="G75" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G75" s="1">
+      <c r="H75" s="1">
         <v>9</v>
       </c>
-      <c r="H75" s="1">
+      <c r="I75" s="1">
         <v>2.5</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J75" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>61</v>
       </c>
@@ -4203,23 +4535,27 @@
       <c r="D76" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="1">
+        <f t="shared" si="2"/>
+        <v>9336801619</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G76" s="1">
+      <c r="H76" s="1">
         <v>14</v>
       </c>
-      <c r="H76" s="1">
+      <c r="I76" s="1">
         <v>4</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J76" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>55</v>
       </c>
@@ -4232,23 +4568,27 @@
       <c r="D77" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="1">
+        <f t="shared" si="2"/>
+        <v>9512293741</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="G77" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G77" s="1">
+      <c r="H77" s="1">
         <v>13</v>
       </c>
-      <c r="H77" s="1">
+      <c r="I77" s="1">
         <v>2.9</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J77" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>50</v>
       </c>
@@ -4261,23 +4601,27 @@
       <c r="D78" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="1">
+        <f t="shared" si="2"/>
+        <v>9790147183</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="G78" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G78" s="1">
+      <c r="H78" s="1">
         <v>12</v>
       </c>
-      <c r="H78" s="1">
+      <c r="I78" s="1">
         <v>2.6</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J78" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>45</v>
       </c>
@@ -4290,23 +4634,27 @@
       <c r="D79" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="1">
+        <f t="shared" si="2"/>
+        <v>9588229686</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="G79" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G79" s="1">
+      <c r="H79" s="1">
         <v>8</v>
       </c>
-      <c r="H79" s="1">
+      <c r="I79" s="1">
         <v>3.3</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J79" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>39</v>
       </c>
@@ -4319,23 +4667,27 @@
       <c r="D80" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="1">
+        <f t="shared" si="2"/>
+        <v>9604988121</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G80" s="1">
+      <c r="H80" s="1">
         <v>6</v>
       </c>
-      <c r="H80" s="1">
+      <c r="I80" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="I80" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J80" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>33</v>
       </c>
@@ -4348,23 +4700,27 @@
       <c r="D81" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="1">
+        <f t="shared" si="2"/>
+        <v>9143226844</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="G81" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G81" s="1">
+      <c r="H81" s="1">
         <v>14</v>
       </c>
-      <c r="H81" s="1">
+      <c r="I81" s="1">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I81" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J81" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>28</v>
       </c>
@@ -4377,23 +4733,27 @@
       <c r="D82" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="1">
+        <f t="shared" si="2"/>
+        <v>9222824732</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="G82" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G82" s="1">
+      <c r="H82" s="1">
         <v>4</v>
       </c>
-      <c r="H82" s="1">
+      <c r="I82" s="1">
         <v>3.7</v>
       </c>
-      <c r="I82" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J82" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>23</v>
       </c>
@@ -4404,23 +4764,27 @@
       <c r="D83" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="1">
+        <f t="shared" si="2"/>
+        <v>9903079055</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="G83" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="G83" s="1">
-        <v>4</v>
       </c>
       <c r="H83" s="1">
         <v>4</v>
       </c>
-      <c r="I83" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I83" s="1">
+        <v>4</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>18</v>
       </c>
@@ -4433,23 +4797,27 @@
       <c r="D84" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E84" s="1" t="s">
+      <c r="E84" s="1">
+        <f t="shared" si="2"/>
+        <v>9434961542</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="G84" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="1">
+      <c r="H84" s="1">
         <v>11</v>
       </c>
-      <c r="H84" s="1">
+      <c r="I84" s="1">
         <v>2.6</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J84" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>12</v>
       </c>
@@ -4462,23 +4830,27 @@
       <c r="D85" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="1">
+        <f t="shared" si="2"/>
+        <v>9991819497</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="G85" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G85" s="1">
+      <c r="H85" s="1">
         <v>3</v>
       </c>
-      <c r="H85" s="1">
+      <c r="I85" s="1">
         <v>4</v>
       </c>
-      <c r="I85" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J85" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>6</v>
       </c>
@@ -4491,19 +4863,23 @@
       <c r="D86" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E86" s="1" t="s">
+      <c r="E86" s="1">
+        <f t="shared" si="2"/>
+        <v>9707665448</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="G86" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G86" s="1">
+      <c r="H86" s="1">
         <v>14</v>
       </c>
-      <c r="H86" s="1">
+      <c r="I86" s="1">
         <v>2.8</v>
       </c>
-      <c r="I86" s="1" t="s">
+      <c r="J86" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -4517,15 +4893,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B68A860D-5914-4E2B-8705-8242C65F669D}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="2" max="3" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>442</v>
       </c>
@@ -4539,7 +4915,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>439</v>
       </c>
@@ -4553,7 +4929,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>436</v>
       </c>
@@ -4567,7 +4943,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>433</v>
       </c>
@@ -4576,6 +4952,20 @@
       </c>
       <c r="D4" t="s">
         <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C5" t="s">
+        <v>451</v>
+      </c>
+      <c r="D5" t="s">
+        <v>452</v>
       </c>
     </row>
   </sheetData>
